--- a/artfynd/A 23598-2026 artfynd.xlsx
+++ b/artfynd/A 23598-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4996361</v>
+        <v>134203496</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lund, 300m VNV om gården Kvarndalen, Boh</t>
+          <t>Kode, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320215.1907236266</v>
+        <v>320378</v>
       </c>
       <c r="R2" t="n">
-        <v>6427188.363285944</v>
+        <v>6427231</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-03-26</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-03-26</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Solberga, Skog</t>
+          <t>Hack på låga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,54 +783,51 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Flora Bohuslän</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Flora Bohuslän</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134203496</v>
+        <v>134203689</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>56904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320378</v>
+        <v>320467</v>
       </c>
       <c r="R3" t="n">
-        <v>6427231</v>
+        <v>6427328</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack på låga.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,6 +905,210 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4996361</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lund, 300m VNV om gården Kvarndalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>320215</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427188</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2000-03-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2000-03-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Solberga, Skog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4997881</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsbryn, 50m N om gården Kvarndalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>320456</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427131</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2000-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-08-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Solberga, Skog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
